--- a/artfynd/A 11483-2025 artfynd.xlsx
+++ b/artfynd/A 11483-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>99182255</v>
       </c>
       <c r="B2" t="n">
-        <v>96943</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99223</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597964.1097595568</v>
+        <v>597964</v>
       </c>
       <c r="R2" t="n">
-        <v>6714425.183804636</v>
+        <v>6714425</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>1998-07-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1998-07-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 11483-2025 artfynd.xlsx
+++ b/artfynd/A 11483-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99182255</v>
       </c>
       <c r="B2" t="n">
-        <v>99223</v>
+        <v>99229</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11483-2025 artfynd.xlsx
+++ b/artfynd/A 11483-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99182255</v>
       </c>
       <c r="B2" t="n">
-        <v>99229</v>
+        <v>99232</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11483-2025 artfynd.xlsx
+++ b/artfynd/A 11483-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99182255</v>
       </c>
       <c r="B2" t="n">
-        <v>99232</v>
+        <v>99237</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11483-2025 artfynd.xlsx
+++ b/artfynd/A 11483-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99182255</v>
       </c>
       <c r="B2" t="n">
-        <v>99237</v>
+        <v>99238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11483-2025 artfynd.xlsx
+++ b/artfynd/A 11483-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99182255</v>
       </c>
       <c r="B2" t="n">
-        <v>99238</v>
+        <v>99265</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11483-2025 artfynd.xlsx
+++ b/artfynd/A 11483-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99182255</v>
       </c>
       <c r="B2" t="n">
-        <v>99265</v>
+        <v>99271</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11483-2025 artfynd.xlsx
+++ b/artfynd/A 11483-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99182255</v>
       </c>
       <c r="B2" t="n">
-        <v>99271</v>
+        <v>99278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
